--- a/dados/gerencial/consolidado_gerencial_2026.xlsx
+++ b/dados/gerencial/consolidado_gerencial_2026.xlsx
@@ -491,16 +491,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="D4" t="n">
         <v>269</v>
       </c>
       <c r="E4" t="n">
-        <v>2777589.11</v>
+        <v>2845800.18</v>
       </c>
       <c r="F4" t="n">
-        <v>2006849.53</v>
+        <v>1958262.33</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>46062</v>
@@ -516,16 +516,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="D5" t="n">
         <v>57</v>
       </c>
       <c r="E5" t="n">
-        <v>1789854.29</v>
+        <v>2080863.54</v>
       </c>
       <c r="F5" t="n">
-        <v>1286609.29</v>
+        <v>1461398.32</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>46065</v>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="D6" t="n">
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>523538.66</v>
+        <v>417143.11</v>
       </c>
       <c r="F6" t="n">
-        <v>275027.6</v>
+        <v>294746.38</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>46069</v>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>518</v>
+        <v>420</v>
       </c>
       <c r="D7" t="n">
         <v>239</v>
       </c>
       <c r="E7" t="n">
-        <v>2717917.47</v>
+        <v>2681452.89</v>
       </c>
       <c r="F7" t="n">
-        <v>1777472.8</v>
+        <v>1745212.26</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>46090</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="8">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
         <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>2051472.53</v>
+        <v>1709185.16</v>
       </c>
       <c r="F8" t="n">
-        <v>1180527.13</v>
+        <v>1214502.29</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="9">
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D9" t="n">
         <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>423897.65</v>
+        <v>420724.69</v>
       </c>
       <c r="F9" t="n">
-        <v>258288.55</v>
+        <v>308541.95</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>46091</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="10">
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
       </c>
       <c r="E10" t="n">
-        <v>2740105.78</v>
+        <v>2896617.12</v>
       </c>
       <c r="F10" t="n">
-        <v>2321194.4</v>
+        <v>1882389.89</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>46126</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="11">
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D11" t="n">
         <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>1734056.86</v>
+        <v>1782996.44</v>
       </c>
       <c r="F11" t="n">
-        <v>1237021.7</v>
+        <v>1465202.95</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>46127</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="12">
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
         <v>45</v>
       </c>
       <c r="E12" t="n">
-        <v>587438.86</v>
+        <v>469320.09</v>
       </c>
       <c r="F12" t="n">
-        <v>362693.66</v>
+        <v>298271.27</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>46125</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="13">
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="D13" t="n">
         <v>240</v>
       </c>
       <c r="E13" t="n">
-        <v>2898676.93</v>
+        <v>2974016.27</v>
       </c>
       <c r="F13" t="n">
-        <v>1923266.6</v>
+        <v>2273246.38</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="14">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
       </c>
       <c r="E14" t="n">
-        <v>2132846.15</v>
+        <v>2138377.05</v>
       </c>
       <c r="F14" t="n">
-        <v>1231621.55</v>
+        <v>1401681.87</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>488045.63</v>
+        <v>505067.3</v>
       </c>
       <c r="F15" t="n">
-        <v>384030.78</v>
+        <v>308607.65</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>46156</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="16">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="D16" t="n">
         <v>264</v>
       </c>
       <c r="E16" t="n">
-        <v>2846764.12</v>
+        <v>2877055.67</v>
       </c>
       <c r="F16" t="n">
-        <v>2333812.74</v>
+        <v>1853063.31</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
     </row>
     <row r="17">
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="D17" t="n">
         <v>43</v>
       </c>
       <c r="E17" t="n">
-        <v>1802107.05</v>
+        <v>1792003.03</v>
       </c>
       <c r="F17" t="n">
-        <v>1498806.94</v>
+        <v>1196439.61</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>46188</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
         <v>41</v>
       </c>
       <c r="E18" t="n">
-        <v>503035.81</v>
+        <v>516158.72</v>
       </c>
       <c r="F18" t="n">
-        <v>328970.11</v>
+        <v>375183.82</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="19">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>597</v>
+        <v>505</v>
       </c>
       <c r="D19" t="n">
         <v>301</v>
       </c>
       <c r="E19" t="n">
-        <v>3345778.24</v>
+        <v>3960516.61</v>
       </c>
       <c r="F19" t="n">
-        <v>2127494.18</v>
+        <v>2244165.82</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>46217</v>
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="D20" t="n">
         <v>46</v>
       </c>
       <c r="E20" t="n">
-        <v>1147534.59</v>
+        <v>1128951.83</v>
       </c>
       <c r="F20" t="n">
-        <v>711403.84</v>
+        <v>726275.1899999999</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D21" t="n">
         <v>49</v>
       </c>
       <c r="E21" t="n">
-        <v>452748.67</v>
+        <v>458505.78</v>
       </c>
       <c r="F21" t="n">
-        <v>345237.98</v>
+        <v>351902.96</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="22">
@@ -941,16 +941,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="D22" t="n">
         <v>218</v>
       </c>
       <c r="E22" t="n">
-        <v>3476550.27</v>
+        <v>3522742.85</v>
       </c>
       <c r="F22" t="n">
-        <v>2856973.34</v>
+        <v>2370065.54</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>46244</v>
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="D23" t="n">
         <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>888733.16</v>
+        <v>903167.12</v>
       </c>
       <c r="F23" t="n">
-        <v>617178.12</v>
+        <v>718872.8100000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="24">
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D24" t="n">
         <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>339631.2</v>
+        <v>401795.67</v>
       </c>
       <c r="F24" t="n">
-        <v>253236.97</v>
+        <v>267266.55</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="25">
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="D25" t="n">
         <v>135</v>
       </c>
       <c r="E25" t="n">
-        <v>3451183.9</v>
+        <v>3655799.59</v>
       </c>
       <c r="F25" t="n">
-        <v>2941588.83</v>
+        <v>2929447.87</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>46274</v>
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D26" t="n">
         <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>1151356.41</v>
+        <v>1141753.3</v>
       </c>
       <c r="F26" t="n">
-        <v>747077.23</v>
+        <v>606075.92</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>46274</v>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D27" t="n">
         <v>28</v>
       </c>
       <c r="E27" t="n">
-        <v>521462.37</v>
+        <v>411820.9</v>
       </c>
       <c r="F27" t="n">
-        <v>290791.88</v>
+        <v>333860.7</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>46274</v>
@@ -1091,10 +1091,10 @@
         <v>2520</v>
       </c>
       <c r="E28" t="n">
-        <v>40792325.71</v>
+        <v>41691834.91</v>
       </c>
       <c r="F28" t="n">
-        <v>29297175.75</v>
+        <v>28584683.64</v>
       </c>
     </row>
   </sheetData>
